--- a/Data/FlightPlan/FPL_10OCT26.xlsx
+++ b/Data/FlightPlan/FPL_10OCT26.xlsx
@@ -803,6 +803,9 @@
     <t>06:35</t>
   </si>
   <si>
+    <t>08:16</t>
+  </si>
+  <si>
     <t>10:15</t>
   </si>
   <si>
@@ -827,6 +830,9 @@
     <t>10:40</t>
   </si>
   <si>
+    <t>11:12</t>
+  </si>
+  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -851,6 +857,9 @@
     <t>VN-A643</t>
   </si>
   <si>
+    <t>08:57</t>
+  </si>
+  <si>
     <t>18:40</t>
   </si>
   <si>
@@ -935,75 +944,78 @@
     <t>10:10</t>
   </si>
   <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:44</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>LJG</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
     <t>16:00</t>
   </si>
   <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>LJG</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
     <t>03:10</t>
   </si>
   <si>
@@ -1037,6 +1049,9 @@
     <t>VN-A668</t>
   </si>
   <si>
+    <t>08:36</t>
+  </si>
+  <si>
     <t>ENH</t>
   </si>
   <si>
@@ -1046,9 +1061,6 @@
     <t>08:20</t>
   </si>
   <si>
-    <t>VCL</t>
-  </si>
-  <si>
     <t>PKX</t>
   </si>
   <si>
@@ -1118,6 +1130,9 @@
     <t>VN-A677</t>
   </si>
   <si>
+    <t>07:26</t>
+  </si>
+  <si>
     <t>17:55</t>
   </si>
   <si>
@@ -1139,9 +1154,6 @@
     <t>VN-A684</t>
   </si>
   <si>
-    <t>08:09</t>
-  </si>
-  <si>
     <t>10:55</t>
   </si>
   <si>
@@ -1268,7 +1280,7 @@
     <t>Total Record(s): 374</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 10, 2026 06:21</t>
+    <t xml:space="preserve">Generated on  Oct 10, 2026 06:46</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -7305,7 +7317,9 @@
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
-      <c r="M188" s="7"/>
+      <c t="s" r="M188" s="7">
+        <v>264</v>
+      </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c t="s" r="A189" s="6">
@@ -7334,7 +7348,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7466,7 +7480,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7499,7 +7513,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7532,7 +7546,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7565,7 +7579,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7577,10 +7591,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7598,7 +7612,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7631,7 +7645,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7640,7 +7654,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>41</v>
@@ -7664,13 +7678,13 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>64</v>
@@ -7712,7 +7726,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7727,11 +7741,13 @@
         <v>206</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
-      <c r="M202" s="7"/>
+      <c t="s" r="M202" s="7">
+        <v>273</v>
+      </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c t="s" r="A203" s="6">
@@ -7745,7 +7761,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7778,7 +7794,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7826,7 +7842,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7838,7 +7854,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>186</v>
@@ -7846,7 +7862,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -7861,7 +7877,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7894,7 +7910,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7906,7 +7922,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>92</v>
@@ -7927,7 +7943,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7960,7 +7976,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8008,7 +8024,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8041,7 +8057,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8074,7 +8090,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8083,10 +8099,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>58</v>
@@ -8107,13 +8123,13 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>64</v>
@@ -8155,7 +8171,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8164,7 +8180,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="I217" s="7">
         <v>197</v>
@@ -8174,7 +8190,9 @@
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
-      <c r="M217" s="7"/>
+      <c t="s" r="M217" s="7">
+        <v>282</v>
+      </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c t="s" r="A218" s="6">
@@ -8188,13 +8206,13 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
+        <v>281</v>
+      </c>
+      <c r="F218" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G218" s="8">
         <v>279</v>
-      </c>
-      <c r="F218" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G218" s="8">
-        <v>277</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>64</v>
@@ -8221,7 +8239,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8254,7 +8272,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8287,7 +8305,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8302,7 +8320,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8335,7 +8353,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8370,7 +8388,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8403,7 +8421,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8436,7 +8454,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8451,7 +8469,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8469,7 +8487,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8478,10 +8496,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>36</v>
@@ -8502,13 +8520,13 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>29</v>
@@ -8535,7 +8553,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8550,7 +8568,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8568,7 +8586,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8580,7 +8598,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>244</v>
@@ -8601,7 +8619,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8616,7 +8634,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8649,7 +8667,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8664,7 +8682,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8682,7 +8700,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8715,7 +8733,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8727,7 +8745,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>186</v>
@@ -8763,7 +8781,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8775,7 +8793,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>124</v>
@@ -8796,7 +8814,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8811,7 +8829,7 @@
         <v>212</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8829,7 +8847,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8841,7 +8859,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>261</v>
@@ -8862,7 +8880,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8910,7 +8928,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8922,7 +8940,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>121</v>
@@ -8930,7 +8948,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -8945,7 +8963,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8978,7 +8996,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8993,7 +9011,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9011,7 +9029,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9044,7 +9062,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9077,7 +9095,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9110,7 +9128,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9158,7 +9176,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9173,7 +9191,7 @@
         <v>186</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9191,7 +9209,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9206,7 +9224,7 @@
         <v>143</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9224,7 +9242,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9257,7 +9275,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9272,7 +9290,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9305,7 +9323,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9340,7 +9358,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9355,14 +9373,14 @@
         <v>164</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="K256" s="7">
         <v>90</v>
       </c>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9377,7 +9395,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9414,7 +9432,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9426,7 +9444,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>230</v>
@@ -9451,7 +9469,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9460,13 +9478,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9484,13 +9502,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>46</v>
@@ -9517,7 +9535,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9526,13 +9544,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9550,22 +9568,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9598,7 +9616,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9610,7 +9628,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>66</v>
@@ -9624,14 +9642,14 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -9640,13 +9658,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9657,29 +9675,29 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>219</v>
+        <v>94</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9697,7 +9715,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -9706,7 +9724,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>26</v>
@@ -9730,19 +9748,19 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>204</v>
@@ -9778,7 +9796,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9790,7 +9808,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>206</v>
@@ -9798,7 +9816,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -9813,7 +9831,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9846,7 +9864,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9858,7 +9876,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>91</v>
@@ -9879,7 +9897,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9891,7 +9909,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>39</v>
@@ -9912,7 +9930,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9927,7 +9945,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9945,7 +9963,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9957,7 +9975,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>116</v>
@@ -9993,7 +10011,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10005,7 +10023,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>19</v>
@@ -10028,7 +10046,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10040,7 +10058,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>255</v>
@@ -10061,7 +10079,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10070,10 +10088,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>35</v>
@@ -10094,13 +10112,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>64</v>
@@ -10127,7 +10145,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10136,7 +10154,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>112</v>
@@ -10160,19 +10178,19 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>115</v>
@@ -10193,7 +10211,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10202,13 +10220,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10226,22 +10244,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10274,7 +10292,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10286,7 +10304,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>121</v>
@@ -10294,7 +10312,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10309,7 +10327,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10318,7 +10336,7 @@
         <v>162</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>20</v>
@@ -10342,13 +10360,13 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>162</v>
@@ -10357,7 +10375,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10375,7 +10393,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10408,7 +10426,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10420,7 +10438,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>40</v>
@@ -10441,7 +10459,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10489,7 +10507,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10498,13 +10516,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10522,13 +10540,13 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>64</v>
@@ -10555,7 +10573,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10570,7 +10588,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10588,7 +10606,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10600,7 +10618,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>83</v>
@@ -10621,7 +10639,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10630,7 +10648,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>233</v>
@@ -10669,7 +10687,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10702,7 +10720,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10714,7 +10732,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>66</v>
@@ -10735,7 +10753,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10747,7 +10765,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>134</v>
@@ -10768,7 +10786,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10780,7 +10798,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>69</v>
@@ -10801,7 +10819,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10813,7 +10831,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>163</v>
@@ -10849,7 +10867,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10861,10 +10879,10 @@
         <v>142</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10882,7 +10900,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10915,7 +10933,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10924,13 +10942,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="I307" s="7">
         <v>94</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10948,13 +10966,13 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>46</v>
@@ -10996,7 +11014,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11008,17 +11026,17 @@
         <v>64</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>208</v>
       </c>
       <c t="s" r="K310" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11033,7 +11051,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11042,7 +11060,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>164</v>
@@ -11066,13 +11084,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>64</v>
@@ -11099,7 +11117,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11108,7 +11126,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>40</v>
@@ -11132,13 +11150,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>64</v>
@@ -11180,7 +11198,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11195,11 +11213,13 @@
         <v>61</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
-      <c r="M316" s="7"/>
+      <c t="s" r="M316" s="7">
+        <v>346</v>
+      </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
       <c t="s" r="A317" s="6">
@@ -11213,7 +11233,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11246,7 +11266,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11255,13 +11275,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11279,13 +11299,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>64</v>
@@ -11327,7 +11347,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11336,7 +11356,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>84</v>
@@ -11362,13 +11382,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>46</v>
@@ -11377,7 +11397,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11395,7 +11415,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11404,13 +11424,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>122</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11428,13 +11448,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>46</v>
@@ -11454,14 +11474,14 @@
         <v>13</v>
       </c>
       <c r="B325" s="7">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c t="s" r="C325" s="7">
         <v>14</v>
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11470,13 +11490,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>345</v>
+        <v>259</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11487,29 +11507,29 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>345</v>
+        <v>259</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>210</v>
+        <v>334</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>94</v>
+        <v>219</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11527,7 +11547,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11536,7 +11556,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>135</v>
@@ -11560,22 +11580,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11608,7 +11628,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11617,13 +11637,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11658,13 +11678,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>64</v>
@@ -11691,7 +11711,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11703,7 +11723,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>56</v>
@@ -11724,7 +11744,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11736,7 +11756,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>148</v>
@@ -11757,7 +11777,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11772,7 +11792,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11805,7 +11825,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11814,18 +11834,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -11840,13 +11860,13 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>46</v>
@@ -11873,7 +11893,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11906,7 +11926,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11939,7 +11959,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11948,7 +11968,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>217</v>
@@ -11972,13 +11992,13 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>46</v>
@@ -11987,7 +12007,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12005,7 +12025,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12014,7 +12034,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>114</v>
@@ -12038,13 +12058,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>46</v>
@@ -12071,7 +12091,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12083,10 +12103,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12119,7 +12139,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12152,7 +12172,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12185,7 +12205,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12194,10 +12214,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>117</v>
@@ -12218,22 +12238,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12266,7 +12286,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12314,7 +12334,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12323,10 +12343,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>241</v>
@@ -12334,7 +12354,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12349,13 +12369,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>64</v>
@@ -12382,7 +12402,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12394,7 +12414,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>98</v>
@@ -12415,7 +12435,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12448,7 +12468,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12457,13 +12477,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12481,13 +12501,13 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>64</v>
@@ -12496,7 +12516,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12529,7 +12549,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12538,7 +12558,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I361" s="7">
         <v>61</v>
@@ -12548,7 +12568,9 @@
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
+      <c t="s" r="M361" s="7">
+        <v>373</v>
+      </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
       <c t="s" r="A362" s="6">
@@ -12562,13 +12584,13 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>46</v>
@@ -12595,7 +12617,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12628,7 +12650,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12661,7 +12683,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12670,10 +12692,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>126</v>
@@ -12694,13 +12716,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>46</v>
@@ -12727,7 +12749,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12760,7 +12782,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12772,10 +12794,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12808,13 +12830,13 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>64</v>
@@ -12823,7 +12845,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12841,7 +12863,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12856,7 +12878,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12874,7 +12896,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12889,7 +12911,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12907,7 +12929,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12919,10 +12941,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12940,7 +12962,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12952,10 +12974,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12973,7 +12995,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13021,7 +13043,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13033,7 +13055,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>201</v>
@@ -13041,7 +13063,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>376</v>
+        <v>206</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13056,7 +13078,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13071,7 +13093,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13089,7 +13111,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13122,7 +13144,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13155,7 +13177,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13167,10 +13189,10 @@
         <v>232</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13188,7 +13210,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13200,10 +13222,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13236,7 +13258,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13271,7 +13293,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13280,13 +13302,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13304,13 +13326,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>89</v>
@@ -13337,7 +13359,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13346,13 +13368,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>256</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13370,13 +13392,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>89</v>
@@ -13385,7 +13407,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13403,7 +13425,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13415,7 +13437,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>220</v>
@@ -13451,7 +13473,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13463,7 +13485,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>88</v>
@@ -13471,7 +13493,7 @@
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13486,7 +13508,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13519,7 +13541,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13528,13 +13550,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13552,13 +13574,13 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>64</v>
@@ -13585,7 +13607,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13597,7 +13619,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>177</v>
@@ -13618,7 +13640,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13651,7 +13673,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13663,10 +13685,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13684,7 +13706,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13717,7 +13739,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13726,13 +13748,13 @@
         <v>64</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>225</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13750,22 +13772,22 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13798,7 +13820,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -13807,10 +13829,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>32</v>
@@ -13831,19 +13853,19 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>108</v>
@@ -13864,7 +13886,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -13897,7 +13919,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -13912,7 +13934,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13930,7 +13952,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -13939,7 +13961,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>135</v>
@@ -13963,19 +13985,19 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>261</v>
@@ -14011,7 +14033,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14023,10 +14045,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14046,7 +14068,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14079,7 +14101,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14112,7 +14134,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14124,7 +14146,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>73</v>
@@ -14160,7 +14182,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14193,7 +14215,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14205,7 +14227,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>113</v>
@@ -14226,7 +14248,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14241,7 +14263,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14259,7 +14281,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14268,7 +14290,7 @@
         <v>64</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c t="s" r="I417" s="7">
         <v>102</v>
@@ -14292,13 +14314,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>64</v>
@@ -14307,7 +14329,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14340,7 +14362,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14373,7 +14395,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14382,13 +14404,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c t="s" r="I421" s="7">
         <v>193</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14406,13 +14428,13 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>46</v>
@@ -14439,7 +14461,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14472,7 +14494,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14484,7 +14506,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>82</v>
@@ -14520,7 +14542,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -14553,7 +14575,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -14568,7 +14590,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14586,7 +14608,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14598,10 +14620,10 @@
         <v>162</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14619,7 +14641,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
@@ -14660,36 +14682,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B431" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c t="s" r="C431" s="7">
         <v>14</v>
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="I431" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c t="s" r="K431" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -14704,13 +14726,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>87</v>
@@ -14719,7 +14741,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14737,7 +14759,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -14749,13 +14771,13 @@
         <v>46</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>32</v>
       </c>
       <c t="s" r="K433" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
@@ -14789,19 +14811,19 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>133</v>
@@ -14811,7 +14833,7 @@
       </c>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>308</v>
+        <v>334</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -14826,7 +14848,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -14835,13 +14857,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c t="s" r="K436" s="7">
         <v>48</v>
@@ -14878,7 +14900,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
@@ -14887,7 +14909,7 @@
         <v>87</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="I438" s="7">
         <v>99</v>
@@ -14896,7 +14918,7 @@
         <v>43</v>
       </c>
       <c t="s" r="K438" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
@@ -14915,13 +14937,13 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>87</v>
@@ -14930,14 +14952,14 @@
         <v>231</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="K439" s="7">
         <v>173</v>
       </c>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -14967,7 +14989,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
@@ -15000,7 +15022,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
@@ -15009,7 +15031,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c t="s" r="I442" s="7">
         <v>133</v>
@@ -15033,13 +15055,13 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
@@ -15081,7 +15103,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
@@ -15118,7 +15140,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15130,7 +15152,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>153</v>
@@ -15155,7 +15177,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -15164,20 +15186,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c t="s" r="I447" s="7">
         <v>210</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c t="s" r="K447" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15192,13 +15214,13 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>17</v>
@@ -15207,10 +15229,10 @@
         <v>83</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="K448" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
@@ -15244,7 +15266,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -15253,10 +15275,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>78</v>
@@ -15277,16 +15299,16 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c t="s" r="I451" s="7">
         <v>166</v>
@@ -15310,22 +15332,22 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>178</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15358,7 +15380,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15367,10 +15389,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>128</v>
@@ -15391,22 +15413,22 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="H455" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15414,7 +15436,7 @@
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c t="s" r="A456" s="9">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B456" s="9"/>
       <c r="C456" s="9"/>
@@ -15434,7 +15456,7 @@
     <row r="457" ht="65.25" customHeight="1"/>
     <row r="458" ht="16.5" customHeight="1">
       <c t="s" r="A458" s="10">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B458" s="10"/>
       <c r="C458" s="10"/>
@@ -15447,7 +15469,7 @@
       <c r="J458" s="10"/>
       <c r="K458" s="10"/>
       <c t="s" r="L458" s="11">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="M458" s="11"/>
       <c r="N458" s="11"/>

--- a/Data/FlightPlan/FPL_10OCT26.xlsx
+++ b/Data/FlightPlan/FPL_10OCT26.xlsx
@@ -794,7 +794,7 @@
     <t>13:45</t>
   </si>
   <si>
-    <t>13:36</t>
+    <t>13:56</t>
   </si>
   <si>
     <t>VN-A633</t>
@@ -914,9 +914,6 @@
     <t>13:55</t>
   </si>
   <si>
-    <t>13:56</t>
-  </si>
-  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1253,168 +1250,168 @@
     <t>12:51</t>
   </si>
   <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:47</t>
+  </si>
+  <si>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>07:26</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>09:57</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>VN-A693</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>19:31</t>
+  </si>
+  <si>
+    <t>VN-A697</t>
+  </si>
+  <si>
+    <t>14:09</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>VN-A698</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>VN-A699</t>
+  </si>
+  <si>
     <t>14:40</t>
   </si>
   <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:41</t>
-  </si>
-  <si>
-    <t>10:34</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:47</t>
-  </si>
-  <si>
-    <t>13:58</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>07:26</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>10:52</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>09:57</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>VN-A693</t>
-  </si>
-  <si>
-    <t>10:58</t>
-  </si>
-  <si>
-    <t>19:31</t>
-  </si>
-  <si>
-    <t>VN-A697</t>
-  </si>
-  <si>
-    <t>14:09</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>VN-A698</t>
-  </si>
-  <si>
-    <t>08:14</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>VN-A699</t>
-  </si>
-  <si>
     <t>5073D *</t>
   </si>
   <si>
@@ -1508,7 +1505,7 @@
     <t>Total Record(s): 375</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 10, 2026 12:25</t>
+    <t xml:space="preserve">Generated on  Oct 10, 2026 12:30</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2988,7 +2985,7 @@
       </c>
       <c r="L36" s="7"/>
       <c t="s" r="M36" s="7">
-        <v>40</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
@@ -7894,7 +7891,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>301</v>
+        <v>261</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8023,7 +8020,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8038,12 +8035,12 @@
         <v>228</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8058,7 +8055,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8091,7 +8088,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8139,7 +8136,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8151,7 +8148,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>207</v>
@@ -8159,7 +8156,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8174,7 +8171,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8194,7 +8191,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8209,7 +8206,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8221,7 +8218,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>96</v>
@@ -8229,7 +8226,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8244,7 +8241,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8277,7 +8274,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8325,7 +8322,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8345,7 +8342,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8360,7 +8357,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8393,7 +8390,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8402,10 +8399,10 @@
         <v>66</v>
       </c>
       <c t="s" r="H213" s="8">
+        <v>312</v>
+      </c>
+      <c t="s" r="I213" s="7">
         <v>313</v>
-      </c>
-      <c t="s" r="I213" s="7">
-        <v>314</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>60</v>
@@ -8426,13 +8423,13 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>66</v>
@@ -8474,7 +8471,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8483,7 +8480,7 @@
         <v>66</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>218</v>
@@ -8494,7 +8491,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8509,13 +8506,13 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>66</v>
@@ -8529,7 +8526,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8544,7 +8541,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8564,7 +8561,7 @@
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8579,7 +8576,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8612,7 +8609,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8660,7 +8657,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8695,7 +8692,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8730,7 +8727,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8750,7 +8747,7 @@
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8765,7 +8762,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8780,12 +8777,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8800,7 +8797,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8809,10 +8806,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>36</v>
@@ -8833,13 +8830,13 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>27</v>
@@ -8866,7 +8863,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8899,7 +8896,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8911,7 +8908,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>267</v>
@@ -8932,7 +8929,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8947,7 +8944,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8980,7 +8977,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9000,7 +8997,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9015,7 +9012,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9048,7 +9045,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9060,7 +9057,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>207</v>
@@ -9096,7 +9093,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9108,7 +9105,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>242</v>
@@ -9116,7 +9113,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9131,7 +9128,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9146,7 +9143,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9164,7 +9161,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9176,7 +9173,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>291</v>
@@ -9197,7 +9194,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9245,7 +9242,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9257,7 +9254,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>127</v>
@@ -9265,7 +9262,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9280,7 +9277,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9315,7 +9312,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9330,12 +9327,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9350,7 +9347,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9387,7 +9384,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9424,7 +9421,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9457,7 +9454,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9505,7 +9502,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9540,7 +9537,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9575,7 +9572,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9608,7 +9605,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9623,7 +9620,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9641,7 +9638,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9653,10 +9650,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I253" s="7">
+        <v>338</v>
+      </c>
+      <c t="s" r="J253" s="7">
         <v>339</v>
-      </c>
-      <c t="s" r="J253" s="7">
-        <v>340</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9674,7 +9671,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9686,10 +9683,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I254" s="7">
+        <v>340</v>
+      </c>
+      <c t="s" r="J254" s="7">
         <v>341</v>
-      </c>
-      <c t="s" r="J254" s="7">
-        <v>342</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9722,7 +9719,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9757,7 +9754,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9772,14 +9769,14 @@
         <v>182</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c t="s" r="K257" s="7">
         <v>93</v>
       </c>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9794,7 +9791,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9831,7 +9828,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9843,7 +9840,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>250</v>
@@ -9868,7 +9865,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9877,7 +9874,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="I260" s="7">
         <v>39</v>
@@ -9901,13 +9898,13 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>47</v>
@@ -9934,7 +9931,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9943,13 +9940,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H262" s="8">
+        <v>345</v>
+      </c>
+      <c t="s" r="I262" s="7">
         <v>346</v>
       </c>
-      <c t="s" r="I262" s="7">
+      <c t="s" r="J262" s="7">
         <v>347</v>
-      </c>
-      <c t="s" r="J262" s="7">
-        <v>348</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9967,22 +9964,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I263" s="7">
+        <v>348</v>
+      </c>
+      <c t="s" r="J263" s="7">
         <v>349</v>
-      </c>
-      <c t="s" r="J263" s="7">
-        <v>350</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -10015,7 +10012,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -10027,7 +10024,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>68</v>
@@ -10035,7 +10032,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10050,7 +10047,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -10059,7 +10056,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>55</v>
@@ -10083,13 +10080,13 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>47</v>
@@ -10116,7 +10113,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10125,7 +10122,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>24</v>
@@ -10149,19 +10146,19 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
+        <v>354</v>
+      </c>
+      <c t="s" r="H269" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I269" s="7">
         <v>355</v>
-      </c>
-      <c t="s" r="H269" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I269" s="7">
-        <v>356</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>226</v>
@@ -10197,7 +10194,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10209,7 +10206,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>228</v>
@@ -10217,7 +10214,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10232,7 +10229,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10252,7 +10249,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10267,7 +10264,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10279,7 +10276,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>95</v>
@@ -10287,7 +10284,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10302,7 +10299,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10335,7 +10332,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10368,7 +10365,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10380,7 +10377,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>122</v>
@@ -10416,7 +10413,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10428,10 +10425,10 @@
         <v>90</v>
       </c>
       <c t="s" r="I278" s="7">
+        <v>362</v>
+      </c>
+      <c t="s" r="J278" s="7">
         <v>363</v>
-      </c>
-      <c t="s" r="J278" s="7">
-        <v>364</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10451,7 +10448,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10463,7 +10460,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>181</v>
@@ -10471,7 +10468,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10486,7 +10483,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10495,18 +10492,18 @@
         <v>66</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>230</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10521,13 +10518,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>66</v>
@@ -10554,7 +10551,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10569,7 +10566,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10587,7 +10584,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10599,7 +10596,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>86</v>
@@ -10620,7 +10617,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10629,7 +10626,7 @@
         <v>66</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c t="s" r="I284" s="7">
         <v>255</v>
@@ -10668,7 +10665,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10680,7 +10677,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>127</v>
@@ -10688,7 +10685,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10703,7 +10700,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10715,7 +10712,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>18</v>
@@ -10723,7 +10720,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10738,7 +10735,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10753,14 +10750,14 @@
         <v>142</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c t="s" r="K288" s="7">
         <v>180</v>
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10775,7 +10772,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10797,7 +10794,7 @@
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10812,7 +10809,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10849,7 +10846,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10901,7 +10898,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10913,7 +10910,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>35</v>
@@ -10921,7 +10918,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -10936,7 +10933,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10969,7 +10966,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10978,7 +10975,7 @@
         <v>66</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>117</v>
@@ -11002,13 +10999,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>66</v>
@@ -11035,7 +11032,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11044,13 +11041,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H297" s="8">
+        <v>380</v>
+      </c>
+      <c t="s" r="I297" s="7">
+        <v>370</v>
+      </c>
+      <c t="s" r="J297" s="7">
         <v>381</v>
-      </c>
-      <c t="s" r="I297" s="7">
-        <v>371</v>
-      </c>
-      <c t="s" r="J297" s="7">
-        <v>382</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -11068,22 +11065,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I298" s="7">
+        <v>382</v>
+      </c>
+      <c t="s" r="J298" s="7">
         <v>383</v>
-      </c>
-      <c t="s" r="J298" s="7">
-        <v>384</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11116,7 +11113,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11136,7 +11133,7 @@
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11151,7 +11148,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11163,7 +11160,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>68</v>
@@ -11186,7 +11183,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11198,7 +11195,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>243</v>
@@ -11219,7 +11216,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11231,7 +11228,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>72</v>
@@ -11252,7 +11249,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11264,7 +11261,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>180</v>
@@ -11300,7 +11297,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11312,15 +11309,15 @@
         <v>150</v>
       </c>
       <c t="s" r="I306" s="7">
+        <v>389</v>
+      </c>
+      <c t="s" r="J306" s="7">
         <v>390</v>
-      </c>
-      <c t="s" r="J306" s="7">
-        <v>391</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11335,7 +11332,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11355,7 +11352,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11370,7 +11367,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11379,7 +11376,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>99</v>
@@ -11403,13 +11400,13 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>47</v>
@@ -11451,7 +11448,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11463,17 +11460,17 @@
         <v>66</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>186</v>
       </c>
       <c t="s" r="K311" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11488,7 +11485,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11497,7 +11494,7 @@
         <v>66</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>182</v>
@@ -11523,13 +11520,13 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>66</v>
@@ -11538,7 +11535,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11556,7 +11553,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11565,7 +11562,7 @@
         <v>66</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>41</v>
@@ -11589,13 +11586,13 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>66</v>
@@ -11637,7 +11634,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11652,12 +11649,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11672,7 +11669,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11707,7 +11704,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11716,13 +11713,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11740,13 +11737,13 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>66</v>
@@ -11788,7 +11785,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11797,7 +11794,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>87</v>
@@ -11823,13 +11820,13 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>47</v>
@@ -11838,12 +11835,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11858,7 +11855,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11867,7 +11864,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="I324" s="7">
         <v>128</v>
@@ -11878,7 +11875,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -11893,13 +11890,13 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>47</v>
@@ -11913,7 +11910,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -11928,7 +11925,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11961,7 +11958,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11973,7 +11970,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>238</v>
@@ -11994,7 +11991,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12003,7 +12000,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c t="s" r="I328" s="7">
         <v>178</v>
@@ -12027,22 +12024,22 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -12075,7 +12072,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12084,13 +12081,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12125,13 +12122,13 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>66</v>
@@ -12145,7 +12142,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12153,14 +12150,14 @@
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>145</v>
+        <v>525</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12169,13 +12166,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12186,29 +12183,29 @@
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>331</v>
+        <v>528</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>415</v>
+        <v>99</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12219,29 +12216,29 @@
         <v>13</v>
       </c>
       <c r="B336" s="7">
-        <v>328</v>
+        <v>1157</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>416</v>
+        <v>197</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12274,7 +12271,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12283,18 +12280,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12309,13 +12306,13 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>47</v>
@@ -12344,7 +12341,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12364,7 +12361,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12379,7 +12376,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12399,7 +12396,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12414,7 +12411,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12423,7 +12420,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>236</v>
@@ -12447,13 +12444,13 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>47</v>
@@ -12462,7 +12459,7 @@
         <v>242</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12480,7 +12477,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12489,7 +12486,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="I344" s="7">
         <v>120</v>
@@ -12513,13 +12510,13 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>47</v>
@@ -12546,7 +12543,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12558,10 +12555,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12594,7 +12591,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12629,7 +12626,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12662,7 +12659,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12710,7 +12707,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12758,7 +12755,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12767,10 +12764,10 @@
         <v>66</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>263</v>
@@ -12778,7 +12775,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12793,13 +12790,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>66</v>
@@ -12828,7 +12825,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12848,7 +12845,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12863,7 +12860,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12896,7 +12893,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12905,13 +12902,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12929,13 +12926,13 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>66</v>
@@ -12944,7 +12941,7 @@
         <v>210</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12977,7 +12974,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12997,7 +12994,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13012,7 +13009,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13047,7 +13044,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13080,7 +13077,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13113,7 +13110,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13122,10 +13119,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>123</v>
@@ -13146,22 +13143,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
+        <v>427</v>
+      </c>
+      <c r="F366" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G366" s="8">
+        <v>380</v>
+      </c>
+      <c t="s" r="H366" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I366" s="7">
+        <v>430</v>
+      </c>
+      <c t="s" r="J366" s="7">
         <v>431</v>
-      </c>
-      <c r="F366" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G366" s="8">
-        <v>381</v>
-      </c>
-      <c t="s" r="H366" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I366" s="7">
-        <v>433</v>
-      </c>
-      <c t="s" r="J366" s="7">
-        <v>434</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13194,13 +13191,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>66</v>
@@ -13229,7 +13226,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13244,7 +13241,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13262,7 +13259,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13295,7 +13292,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13307,10 +13304,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13328,7 +13325,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13340,10 +13337,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13361,7 +13358,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13409,7 +13406,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13421,7 +13418,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>222</v>
@@ -13444,7 +13441,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13459,12 +13456,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13479,7 +13476,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13512,7 +13509,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13545,7 +13542,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13557,10 +13554,10 @@
         <v>254</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13578,7 +13575,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13590,10 +13587,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13626,7 +13623,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13661,7 +13658,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13673,15 +13670,15 @@
         <v>147</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13696,7 +13693,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13729,7 +13726,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13738,13 +13735,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="I385" s="7">
         <v>132</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13762,13 +13759,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>92</v>
@@ -13777,7 +13774,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13795,7 +13792,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13807,7 +13804,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>239</v>
@@ -13843,7 +13840,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13855,7 +13852,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>91</v>
@@ -13863,7 +13860,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13878,7 +13875,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13913,7 +13910,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13922,13 +13919,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13948,13 +13945,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>66</v>
@@ -13968,7 +13965,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -13983,7 +13980,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14016,7 +14013,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14049,7 +14046,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14064,7 +14061,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -14082,7 +14079,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14115,7 +14112,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14124,13 +14121,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14148,22 +14145,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14196,7 +14193,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14205,10 +14202,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>31</v>
@@ -14216,7 +14213,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14231,19 +14228,19 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>94</v>
@@ -14251,7 +14248,7 @@
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14266,7 +14263,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -14299,7 +14296,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -14314,7 +14311,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14332,7 +14329,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -14341,7 +14338,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="I404" s="7">
         <v>178</v>
@@ -14365,19 +14362,19 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>291</v>
@@ -14413,7 +14410,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14425,10 +14422,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14448,7 +14445,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14468,7 +14465,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14483,7 +14480,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14503,7 +14500,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14518,7 +14515,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14530,7 +14527,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>76</v>
@@ -14566,7 +14563,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14586,7 +14583,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14601,7 +14598,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14613,7 +14610,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>119</v>
@@ -14634,7 +14631,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14649,7 +14646,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14667,7 +14664,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14676,7 +14673,7 @@
         <v>66</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c t="s" r="I415" s="7">
         <v>108</v>
@@ -14700,13 +14697,13 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
+        <v>458</v>
+      </c>
+      <c r="F416" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G416" s="8">
         <v>460</v>
-      </c>
-      <c r="F416" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G416" s="8">
-        <v>462</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>66</v>
@@ -14715,7 +14712,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14748,7 +14745,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14768,7 +14765,7 @@
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -14783,27 +14780,27 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
+        <v>461</v>
+      </c>
+      <c r="F419" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G419" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H419" s="8">
         <v>463</v>
-      </c>
-      <c r="F419" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G419" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H419" s="8">
-        <v>465</v>
       </c>
       <c t="s" r="I419" s="7">
         <v>208</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14818,13 +14815,13 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
+        <v>461</v>
+      </c>
+      <c r="F420" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G420" s="8">
         <v>463</v>
-      </c>
-      <c r="F420" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G420" s="8">
-        <v>465</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>47</v>
@@ -14851,7 +14848,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14863,7 +14860,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>44</v>
@@ -14884,7 +14881,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14917,7 +14914,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14950,7 +14947,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14962,10 +14959,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I424" s="7">
+        <v>338</v>
+      </c>
+      <c t="s" r="J424" s="7">
         <v>339</v>
-      </c>
-      <c t="s" r="J424" s="7">
-        <v>340</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14998,7 +14995,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -15026,14 +15023,14 @@
         <v>13</v>
       </c>
       <c r="B427" s="7">
-        <v>525</v>
+        <v>145</v>
       </c>
       <c t="s" r="C427" s="7">
         <v>14</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15042,13 +15039,13 @@
         <v>66</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>243</v>
+        <v>58</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15059,29 +15056,29 @@
         <v>13</v>
       </c>
       <c r="B428" s="7">
-        <v>528</v>
+        <v>331</v>
       </c>
       <c t="s" r="C428" s="7">
         <v>14</v>
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>99</v>
+        <v>444</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15092,29 +15089,29 @@
         <v>13</v>
       </c>
       <c r="B429" s="7">
-        <v>1157</v>
+        <v>328</v>
       </c>
       <c t="s" r="C429" s="7">
         <v>14</v>
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>197</v>
+        <v>429</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -15140,36 +15137,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B431" s="7">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c t="s" r="C431" s="7">
         <v>14</v>
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
+        <v>469</v>
+      </c>
+      <c t="s" r="H431" s="8">
         <v>470</v>
-      </c>
-      <c t="s" r="H431" s="8">
-        <v>471</v>
       </c>
       <c t="s" r="I431" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c t="s" r="K431" s="7">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -15184,13 +15181,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>90</v>
@@ -15199,7 +15196,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -15217,7 +15214,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -15229,7 +15226,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>233</v>
@@ -15265,19 +15262,19 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>144</v>
@@ -15287,7 +15284,7 @@
       </c>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -15302,7 +15299,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -15311,13 +15308,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c t="s" r="K436" s="7">
         <v>49</v>
@@ -15354,7 +15351,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
@@ -15363,7 +15360,7 @@
         <v>90</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c t="s" r="I438" s="7">
         <v>104</v>
@@ -15372,11 +15369,11 @@
         <v>44</v>
       </c>
       <c t="s" r="K438" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -15391,13 +15388,13 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>90</v>
@@ -15406,14 +15403,14 @@
         <v>252</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c t="s" r="K439" s="7">
         <v>290</v>
       </c>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15443,7 +15440,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
@@ -15463,7 +15460,7 @@
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -15478,7 +15475,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
@@ -15487,7 +15484,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c t="s" r="I442" s="7">
         <v>144</v>
@@ -15498,7 +15495,7 @@
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -15513,13 +15510,13 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>16</v>
@@ -15561,27 +15558,27 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>90</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -15596,7 +15593,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15633,7 +15630,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -15670,7 +15667,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
@@ -15679,20 +15676,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c t="s" r="I448" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c t="s" r="K448" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -15707,13 +15704,13 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c t="s" r="H449" s="8">
         <v>16</v>
@@ -15722,10 +15719,10 @@
         <v>86</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c t="s" r="K449" s="7">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
@@ -15759,7 +15756,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -15768,10 +15765,10 @@
         <v>66</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>81</v>
@@ -15779,7 +15776,7 @@
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -15794,16 +15791,16 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>105</v>
@@ -15827,22 +15824,22 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>198</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15875,7 +15872,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
@@ -15884,7 +15881,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c t="s" r="I455" s="7">
         <v>295</v>
@@ -15895,7 +15892,7 @@
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -15910,22 +15907,22 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15933,7 +15930,7 @@
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c t="s" r="A457" s="9">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B457" s="9"/>
       <c r="C457" s="9"/>
@@ -15953,7 +15950,7 @@
     <row r="458" ht="65.25" customHeight="1"/>
     <row r="459" ht="16.5" customHeight="1">
       <c t="s" r="A459" s="10">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B459" s="10"/>
       <c r="C459" s="10"/>
@@ -15966,7 +15963,7 @@
       <c r="J459" s="10"/>
       <c r="K459" s="10"/>
       <c t="s" r="L459" s="11">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M459" s="11"/>
       <c r="N459" s="11"/>

--- a/Data/FlightPlan/FPL_10OCT26.xlsx
+++ b/Data/FlightPlan/FPL_10OCT26.xlsx
@@ -269,6 +269,9 @@
     <t>16:15</t>
   </si>
   <si>
+    <t>16:05</t>
+  </si>
+  <si>
     <t>HYD</t>
   </si>
   <si>
@@ -314,9 +317,6 @@
     <t>15:35</t>
   </si>
   <si>
-    <t>16:05</t>
-  </si>
-  <si>
     <t>17:10</t>
   </si>
   <si>
@@ -707,750 +707,759 @@
     <t>10:28</t>
   </si>
   <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>14:57</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>14:24</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>12:42</t>
+  </si>
+  <si>
+    <t>17:01</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>392A *</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:22</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>13:17</t>
+  </si>
+  <si>
+    <t>15:42</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>15:32</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:16</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>13:33</t>
+  </si>
+  <si>
+    <t>16:13</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>09:06</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:23</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>13:13</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>13:08</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:24</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>14:08</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>16:22</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>04:40</t>
+  </si>
+  <si>
+    <t>06:49</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>17:58</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>12:07</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>DYG</t>
+  </si>
+  <si>
     <t>00:10</t>
   </si>
   <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:06</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>LJG</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:12</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:44</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:22</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>12:43</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>10:24</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>11:56</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>15:31</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:47</t>
+  </si>
+  <si>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>07:26</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>17:57</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>09:57</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
     <t>05:55</t>
   </si>
   <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>14:57</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>10:23</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:03</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:08</t>
-  </si>
-  <si>
-    <t>14:24</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>13:56</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>12:42</t>
-  </si>
-  <si>
-    <t>17:01</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>10:42</t>
-  </si>
-  <si>
-    <t>13:32</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>392A *</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:22</t>
-  </si>
-  <si>
-    <t>10:13</t>
-  </si>
-  <si>
-    <t>13:17</t>
-  </si>
-  <si>
-    <t>15:42</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>11:09</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>15:32</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:16</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:49</t>
-  </si>
-  <si>
-    <t>13:33</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>09:06</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>11:12</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:23</t>
-  </si>
-  <si>
-    <t>10:48</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>13:13</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>11:21</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:24</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>14:08</t>
-  </si>
-  <si>
-    <t>17:28</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>16:22</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>04:40</t>
-  </si>
-  <si>
-    <t>06:49</t>
-  </si>
-  <si>
-    <t>11:07</t>
-  </si>
-  <si>
-    <t>15:02</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>12:07</t>
-  </si>
-  <si>
-    <t>13:42</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>12:33</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>DYG</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>08:11</t>
-  </si>
-  <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:06</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>10:37</t>
-  </si>
-  <si>
-    <t>LJG</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:12</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:22</t>
-  </si>
-  <si>
-    <t>11:23</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>12:43</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>15:39</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>10:24</t>
-  </si>
-  <si>
-    <t>13:28</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>08:36</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>16:53</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>11:56</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:41</t>
-  </si>
-  <si>
-    <t>10:34</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:47</t>
-  </si>
-  <si>
-    <t>13:58</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>07:26</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>15:07</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>10:52</t>
-  </si>
-  <si>
-    <t>17:57</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>15:06</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>09:57</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1466,9 +1475,6 @@
     <t>14:09</t>
   </si>
   <si>
-    <t>DEL</t>
-  </si>
-  <si>
     <t>VN-A698</t>
   </si>
   <si>
@@ -1583,7 +1589,7 @@
     <t>Total Record(s): 374</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 10, 2026 14:06</t>
+    <t xml:space="preserve">Generated on  Oct 10, 2026 14:12</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2880,7 +2886,9 @@
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
+      <c t="s" r="M30" s="7">
+        <v>86</v>
+      </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c t="s" r="A31" s="6">
@@ -2903,13 +2911,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H31" s="8">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2933,7 +2941,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G32" s="8">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="H32" s="8">
         <v>48</v>
@@ -2942,7 +2950,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2971,23 +2979,23 @@
         <v>1607</v>
       </c>
       <c t="s" r="C34" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G34" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H34" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J34" s="7">
         <v>79</v>
@@ -3010,7 +3018,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -3019,18 +3027,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I35" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c t="s" r="M35" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -3045,25 +3053,25 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="K36" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L36" s="7"/>
       <c t="s" r="M36" s="7">
@@ -3082,7 +3090,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -3091,13 +3099,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I37" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -3115,19 +3123,19 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c t="s" r="J38" s="7">
         <v>102</v>
@@ -3148,7 +3156,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -3364,7 +3372,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3796,7 +3804,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I60" s="7">
         <v>145</v>
@@ -3826,7 +3834,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>48</v>
@@ -3838,7 +3846,7 @@
         <v>147</v>
       </c>
       <c t="s" r="K61" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
@@ -4591,7 +4599,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>106</v>
@@ -4693,7 +4701,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I89" s="7">
         <v>134</v>
@@ -4723,7 +4731,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>48</v>
@@ -4732,7 +4740,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4807,7 +4815,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I93" s="7">
         <v>201</v>
@@ -4837,7 +4845,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>68</v>
@@ -5407,7 +5415,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>224</v>
@@ -5441,7 +5449,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>68</v>
@@ -5485,7 +5493,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="K115" s="7">
         <v>85</v>
@@ -5583,7 +5591,7 @@
         <v>13</v>
       </c>
       <c r="B119" s="7">
-        <v>1925</v>
+        <v>971</v>
       </c>
       <c t="s" r="C119" s="7">
         <v>14</v>
@@ -5599,13 +5607,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5616,7 +5624,7 @@
         <v>76</v>
       </c>
       <c r="B120" s="7">
-        <v>1926</v>
+        <v>972</v>
       </c>
       <c t="s" r="C120" s="7">
         <v>14</v>
@@ -5629,13 +5637,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>233</v>
@@ -6195,7 +6203,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>255</v>
@@ -6273,7 +6281,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I141" s="7">
         <v>224</v>
@@ -6305,7 +6313,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>24</v>
@@ -6314,7 +6322,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6830,7 +6838,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>121</v>
@@ -6862,7 +6870,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>103</v>
@@ -6892,7 +6900,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>48</v>
@@ -6973,7 +6981,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>48</v>
@@ -7052,7 +7060,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7150,7 +7158,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>285</v>
@@ -7454,7 +7462,7 @@
         <v>297</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>130</v>
@@ -7492,7 +7500,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7524,7 +7532,7 @@
         <v>297</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>133</v>
@@ -7742,10 +7750,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>168</v>
@@ -7774,20 +7782,22 @@
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>253</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
-      <c r="M189" s="7"/>
+      <c t="s" r="M189" s="7">
+        <v>311</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c t="s" r="A190" s="6">
@@ -7882,7 +7892,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7902,7 +7912,7 @@
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7917,7 +7927,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7952,7 +7962,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7964,10 +7974,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7987,7 +7997,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8020,7 +8030,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8053,7 +8063,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8065,7 +8075,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>221</v>
@@ -8101,7 +8111,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8116,12 +8126,12 @@
         <v>235</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8136,7 +8146,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8169,7 +8179,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8217,7 +8227,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8229,7 +8239,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>212</v>
@@ -8237,7 +8247,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8252,7 +8262,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8272,7 +8282,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8287,7 +8297,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8299,15 +8309,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8322,7 +8332,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8355,7 +8365,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8403,7 +8413,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8415,7 +8425,7 @@
         <v>153</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>168</v>
@@ -8423,7 +8433,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8438,7 +8448,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8471,7 +8481,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8480,10 +8490,10 @@
         <v>68</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>62</v>
@@ -8504,13 +8514,13 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>68</v>
@@ -8552,7 +8562,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8561,7 +8571,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>224</v>
@@ -8572,7 +8582,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8587,13 +8597,13 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>68</v>
@@ -8607,7 +8617,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8622,7 +8632,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8637,12 +8647,12 @@
         <v>187</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8657,7 +8667,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8690,7 +8700,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8738,7 +8748,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8750,10 +8760,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8773,7 +8783,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8808,7 +8818,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8817,7 +8827,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I223" s="7">
         <v>213</v>
@@ -8828,7 +8838,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8843,13 +8853,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>28</v>
@@ -8858,12 +8868,12 @@
         <v>33</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8878,7 +8888,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8887,10 +8897,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>37</v>
@@ -8898,7 +8908,7 @@
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8913,13 +8923,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>28</v>
@@ -8946,7 +8956,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8979,7 +8989,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8991,7 +9001,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>279</v>
@@ -9012,7 +9022,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9027,7 +9037,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -9060,7 +9070,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9075,12 +9085,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9095,7 +9105,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9115,7 +9125,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9130,7 +9140,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9142,7 +9152,7 @@
         <v>114</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>212</v>
@@ -9178,7 +9188,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9190,7 +9200,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>252</v>
@@ -9198,7 +9208,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9213,7 +9223,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9228,7 +9238,7 @@
         <v>196</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9246,7 +9256,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9258,7 +9268,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>304</v>
@@ -9279,7 +9289,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9327,7 +9337,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9339,7 +9349,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>129</v>
@@ -9347,7 +9357,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9362,7 +9372,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9397,7 +9407,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9412,12 +9422,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9432,7 +9442,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9444,13 +9454,13 @@
         <v>28</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>276</v>
       </c>
       <c t="s" r="K243" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
@@ -9469,7 +9479,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9487,11 +9497,11 @@
         <v>73</v>
       </c>
       <c t="s" r="K244" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9506,7 +9516,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9539,7 +9549,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9587,7 +9597,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9622,7 +9632,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9657,7 +9667,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9677,7 +9687,7 @@
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9692,7 +9702,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9707,7 +9717,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9725,7 +9735,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9737,10 +9747,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9758,7 +9768,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9770,10 +9780,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9806,7 +9816,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9818,7 +9828,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>191</v>
@@ -9841,7 +9851,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9856,14 +9866,14 @@
         <v>186</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="K256" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9878,7 +9888,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9900,7 +9910,7 @@
       </c>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9915,7 +9925,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9927,7 +9937,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>260</v>
@@ -9952,7 +9962,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9961,7 +9971,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>40</v>
@@ -9985,13 +9995,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>48</v>
@@ -10018,7 +10028,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10027,13 +10037,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10051,22 +10061,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10099,7 +10109,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -10111,7 +10121,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>70</v>
@@ -10119,7 +10129,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10134,7 +10144,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -10143,7 +10153,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>56</v>
@@ -10169,13 +10179,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>48</v>
@@ -10184,7 +10194,7 @@
         <v>238</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -10202,7 +10212,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -10211,16 +10221,16 @@
         <v>48</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>140</v>
       </c>
       <c t="s" r="K267" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
@@ -10239,13 +10249,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>48</v>
@@ -10254,10 +10264,10 @@
         <v>221</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>232</v>
+        <v>373</v>
       </c>
       <c t="s" r="K268" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
@@ -10291,7 +10301,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10303,7 +10313,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>235</v>
@@ -10311,7 +10321,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10326,7 +10336,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10346,7 +10356,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10361,7 +10371,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10373,15 +10383,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10396,7 +10406,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10416,7 +10426,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10431,7 +10441,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10464,7 +10474,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10476,7 +10486,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>124</v>
@@ -10512,7 +10522,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10521,13 +10531,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10547,19 +10557,19 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>185</v>
@@ -10567,7 +10577,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10582,7 +10592,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10591,18 +10601,18 @@
         <v>68</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>237</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10617,13 +10627,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>68</v>
@@ -10650,7 +10660,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10665,7 +10675,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10683,7 +10693,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10695,10 +10705,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10716,7 +10726,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10725,7 +10735,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c t="s" r="I283" s="7">
         <v>266</v>
@@ -10764,7 +10774,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10776,7 +10786,7 @@
         <v>138</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>129</v>
@@ -10784,7 +10794,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10799,7 +10809,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10811,7 +10821,7 @@
         <v>150</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>18</v>
@@ -10819,7 +10829,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10834,7 +10844,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10849,14 +10859,14 @@
         <v>145</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="K287" s="7">
         <v>184</v>
       </c>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10871,7 +10881,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10883,7 +10893,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>168</v>
@@ -10893,7 +10903,7 @@
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10908,7 +10918,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10917,10 +10927,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>42</v>
@@ -10945,13 +10955,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>48</v>
@@ -10997,7 +11007,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -11009,7 +11019,7 @@
         <v>150</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>36</v>
@@ -11017,7 +11027,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11032,7 +11042,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -11052,7 +11062,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11067,7 +11077,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11076,7 +11086,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>119</v>
@@ -11100,13 +11110,13 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>68</v>
@@ -11133,7 +11143,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11142,13 +11152,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -11166,22 +11176,22 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -11214,7 +11224,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11234,7 +11244,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11249,7 +11259,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11261,7 +11271,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>70</v>
@@ -11284,7 +11294,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11296,7 +11306,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>253</v>
@@ -11304,7 +11314,7 @@
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11319,7 +11329,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11328,10 +11338,10 @@
         <v>68</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>74</v>
@@ -11352,19 +11362,19 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>114</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>184</v>
@@ -11400,7 +11410,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11412,15 +11422,15 @@
         <v>153</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11435,7 +11445,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11447,7 +11457,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>168</v>
@@ -11455,7 +11465,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11470,7 +11480,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11479,7 +11489,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="I307" s="7">
         <v>181</v>
@@ -11503,19 +11513,19 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>304</v>
@@ -11551,7 +11561,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11563,17 +11573,17 @@
         <v>68</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>190</v>
       </c>
       <c t="s" r="K310" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11588,7 +11598,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11597,7 +11607,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>186</v>
@@ -11623,13 +11633,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>68</v>
@@ -11638,7 +11648,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11658,7 +11668,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11667,7 +11677,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>42</v>
@@ -11691,13 +11701,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
+        <v>416</v>
+      </c>
+      <c r="F314" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G314" s="8">
         <v>414</v>
-      </c>
-      <c r="F314" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G314" s="8">
-        <v>412</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>68</v>
@@ -11739,7 +11749,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11754,12 +11764,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11774,7 +11784,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11794,7 +11804,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11809,7 +11819,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11818,18 +11828,18 @@
         <v>68</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>58</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11844,13 +11854,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>68</v>
@@ -11892,7 +11902,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11901,10 +11911,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>224</v>
@@ -11927,13 +11937,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>48</v>
@@ -11942,12 +11952,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11962,7 +11972,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11971,7 +11981,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>130</v>
@@ -11982,7 +11992,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11997,13 +12007,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>48</v>
@@ -12017,7 +12027,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12032,7 +12042,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12065,7 +12075,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12077,7 +12087,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>247</v>
@@ -12098,7 +12108,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12107,7 +12117,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>181</v>
@@ -12131,22 +12141,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -12175,11 +12185,11 @@
         <v>25</v>
       </c>
       <c t="s" r="C330" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12188,13 +12198,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -12225,17 +12235,17 @@
         <v>9953</v>
       </c>
       <c t="s" r="C332" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>68</v>
@@ -12249,7 +12259,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12264,7 +12274,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12283,7 +12293,9 @@
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
-      <c r="M333" s="7"/>
+      <c t="s" r="M333" s="7">
+        <v>435</v>
+      </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
       <c t="s" r="A334" s="6">
@@ -12297,7 +12309,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12309,7 +12321,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>23</v>
@@ -12330,7 +12342,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12378,7 +12390,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12387,18 +12399,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12413,13 +12425,13 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>48</v>
@@ -12448,7 +12460,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12468,7 +12480,7 @@
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12483,7 +12495,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12503,7 +12515,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12518,7 +12530,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12527,7 +12539,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>245</v>
@@ -12551,13 +12563,13 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>48</v>
@@ -12566,7 +12578,7 @@
         <v>252</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12584,7 +12596,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12593,13 +12605,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>122</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12617,13 +12629,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>48</v>
@@ -12650,7 +12662,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12662,10 +12674,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12698,7 +12710,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12733,7 +12745,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12766,7 +12778,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12799,7 +12811,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12811,10 +12823,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12847,7 +12859,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12856,10 +12868,10 @@
         <v>68</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>274</v>
@@ -12867,7 +12879,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12882,13 +12894,13 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>68</v>
@@ -12917,7 +12929,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12926,10 +12938,10 @@
         <v>68</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>105</v>
@@ -12937,7 +12949,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12952,13 +12964,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>68</v>
@@ -12985,7 +12997,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12994,13 +13006,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13018,13 +13030,13 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>68</v>
@@ -13033,7 +13045,7 @@
         <v>215</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13066,7 +13078,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13086,7 +13098,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13101,7 +13113,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13136,7 +13148,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13169,7 +13181,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13202,7 +13214,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13211,10 +13223,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>125</v>
@@ -13235,22 +13247,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13283,13 +13295,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>68</v>
@@ -13298,12 +13310,12 @@
         <v>145</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13318,7 +13330,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13333,12 +13345,12 @@
         <v>168</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13353,7 +13365,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13386,7 +13398,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13398,10 +13410,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13419,7 +13431,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13431,10 +13443,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13452,7 +13464,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13500,7 +13512,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13512,7 +13524,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>230</v>
@@ -13535,7 +13547,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13550,12 +13562,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13570,7 +13582,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13582,7 +13594,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>263</v>
@@ -13590,7 +13602,7 @@
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13605,7 +13617,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13638,7 +13650,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13650,10 +13662,10 @@
         <v>265</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13671,7 +13683,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13683,10 +13695,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13719,7 +13731,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13728,7 +13740,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I380" s="7">
         <v>29</v>
@@ -13754,27 +13766,27 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>150</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13789,7 +13801,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13798,7 +13810,7 @@
         <v>150</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>133</v>
@@ -13809,7 +13821,7 @@
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13824,22 +13836,22 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13857,22 +13869,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13890,19 +13902,19 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>248</v>
@@ -13938,7 +13950,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13950,15 +13962,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>470</v>
+        <v>233</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13973,7 +13985,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14008,7 +14020,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14017,13 +14029,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -14043,13 +14055,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>68</v>
@@ -14063,7 +14075,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14078,7 +14090,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14087,7 +14099,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>300</v>
@@ -14098,7 +14110,7 @@
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14113,13 +14125,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>68</v>
@@ -14146,7 +14158,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14161,7 +14173,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14179,7 +14191,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14212,7 +14224,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14221,13 +14233,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -14245,22 +14257,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14293,7 +14305,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14302,10 +14314,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>32</v>
@@ -14313,7 +14325,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14328,27 +14340,27 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14363,7 +14375,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14398,7 +14410,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -14413,7 +14425,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14431,7 +14443,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -14440,7 +14452,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c t="s" r="I402" s="7">
         <v>25</v>
@@ -14464,22 +14476,22 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>233</v>
+        <v>482</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14512,7 +14524,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14524,10 +14536,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14547,7 +14559,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14567,7 +14579,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14582,7 +14594,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14602,7 +14614,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14617,7 +14629,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14629,7 +14641,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>78</v>
@@ -14665,7 +14677,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14685,7 +14697,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14700,7 +14712,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14712,7 +14724,7 @@
         <v>160</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>121</v>
@@ -14733,7 +14745,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14748,7 +14760,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14759,14 +14771,14 @@
         <v>13</v>
       </c>
       <c r="B413" s="7">
-        <v>971</v>
+        <v>1925</v>
       </c>
       <c t="s" r="C413" s="7">
         <v>14</v>
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14775,13 +14787,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>485</v>
+        <v>61</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14792,29 +14804,29 @@
         <v>76</v>
       </c>
       <c r="B414" s="7">
-        <v>972</v>
+        <v>1926</v>
       </c>
       <c t="s" r="C414" s="7">
         <v>14</v>
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>485</v>
+        <v>61</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>173</v>
+        <v>373</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14847,7 +14859,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14867,7 +14879,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14882,7 +14894,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14891,18 +14903,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c t="s" r="I417" s="7">
         <v>213</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -14917,13 +14929,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>48</v>
@@ -14952,7 +14964,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14964,7 +14976,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>45</v>
@@ -14985,7 +14997,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15018,7 +15030,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15051,7 +15063,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15063,10 +15075,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -15099,7 +15111,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -15114,7 +15126,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -15134,7 +15146,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -15146,7 +15158,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>59</v>
@@ -15167,7 +15179,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -15179,7 +15191,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>161</v>
@@ -15200,7 +15212,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15215,7 +15227,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15241,36 +15253,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B429" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c t="s" r="C429" s="7">
         <v>14</v>
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>126</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c t="s" r="K429" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15285,22 +15297,22 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -15314,23 +15326,23 @@
         <v>607</v>
       </c>
       <c t="s" r="C431" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>242</v>
@@ -15366,29 +15378,29 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>147</v>
       </c>
       <c t="s" r="K433" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15403,7 +15415,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
@@ -15412,13 +15424,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c t="s" r="K434" s="7">
         <v>50</v>
@@ -15455,16 +15467,16 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c t="s" r="I436" s="7">
         <v>106</v>
@@ -15473,11 +15485,11 @@
         <v>45</v>
       </c>
       <c t="s" r="K436" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15492,29 +15504,29 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>263</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c t="s" r="K437" s="7">
         <v>303</v>
       </c>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15544,7 +15556,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
@@ -15564,7 +15576,7 @@
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15579,7 +15591,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15588,7 +15600,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>147</v>
@@ -15599,7 +15611,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15614,13 +15626,13 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>16</v>
@@ -15662,27 +15674,27 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15697,13 +15709,13 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>48</v>
@@ -15719,7 +15731,7 @@
       </c>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15734,7 +15746,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
@@ -15771,7 +15783,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15780,20 +15792,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c t="s" r="I446" s="7">
         <v>238</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c t="s" r="K446" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15808,25 +15820,25 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c t="s" r="K447" s="7">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
@@ -15860,7 +15872,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
@@ -15869,10 +15881,10 @@
         <v>68</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>83</v>
@@ -15880,7 +15892,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -15895,16 +15907,16 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c t="s" r="I450" s="7">
         <v>107</v>
@@ -15928,22 +15940,22 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G451" s="8">
+        <v>520</v>
+      </c>
+      <c t="s" r="H451" s="8">
         <v>518</v>
-      </c>
-      <c t="s" r="H451" s="8">
-        <v>516</v>
       </c>
       <c t="s" r="I451" s="7">
         <v>203</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15976,7 +15988,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
@@ -15985,7 +15997,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>308</v>
@@ -15996,7 +16008,7 @@
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16011,22 +16023,22 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -16034,7 +16046,7 @@
     </row>
     <row r="455" ht="16.5" customHeight="1">
       <c t="s" r="A455" s="9">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
@@ -16054,7 +16066,7 @@
     <row r="456" ht="65.25" customHeight="1"/>
     <row r="457" ht="16.5" customHeight="1">
       <c t="s" r="A457" s="10">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B457" s="10"/>
       <c r="C457" s="10"/>
@@ -16067,7 +16079,7 @@
       <c r="J457" s="10"/>
       <c r="K457" s="10"/>
       <c t="s" r="L457" s="11">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M457" s="11"/>
       <c r="N457" s="11"/>

--- a/Data/FlightPlan/FPL_10OCT26.xlsx
+++ b/Data/FlightPlan/FPL_10OCT26.xlsx
@@ -398,6 +398,9 @@
     <t>18:25</t>
   </si>
   <si>
+    <t>18:26</t>
+  </si>
+  <si>
     <t>19:25</t>
   </si>
   <si>
@@ -623,6 +626,9 @@
     <t>17:15</t>
   </si>
   <si>
+    <t>17:49</t>
+  </si>
+  <si>
     <t>17:45</t>
   </si>
   <si>
@@ -755,6 +761,9 @@
     <t>14:57</t>
   </si>
   <si>
+    <t>17:20</t>
+  </si>
+  <si>
     <t>18:35</t>
   </si>
   <si>
@@ -773,6 +782,9 @@
     <t>14:15</t>
   </si>
   <si>
+    <t>16:18</t>
+  </si>
+  <si>
     <t>NOZ</t>
   </si>
   <si>
@@ -797,6 +809,9 @@
     <t>15:30</t>
   </si>
   <si>
+    <t>16:58</t>
+  </si>
+  <si>
     <t>VDH</t>
   </si>
   <si>
@@ -824,15 +839,12 @@
     <t>14:24</t>
   </si>
   <si>
-    <t>16:41</t>
+    <t>16:47</t>
   </si>
   <si>
     <t>18:30</t>
   </si>
   <si>
-    <t>20:20</t>
-  </si>
-  <si>
     <t>MNL</t>
   </si>
   <si>
@@ -1175,243 +1187,249 @@
     <t>VCL</t>
   </si>
   <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:06</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>17:39</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>LJG</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:12</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:44</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:22</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>12:43</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>10:24</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>15:28</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>17:04</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>11:56</t>
+  </si>
+  <si>
+    <t>15:46</t>
+  </si>
+  <si>
     <t>DYG</t>
   </si>
   <si>
+    <t>17:35</t>
+  </si>
+  <si>
     <t>00:10</t>
   </si>
   <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>08:11</t>
-  </si>
-  <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:06</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>10:37</t>
-  </si>
-  <si>
-    <t>LJG</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:12</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:22</t>
-  </si>
-  <si>
-    <t>11:23</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>12:43</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>15:39</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>10:24</t>
-  </si>
-  <si>
-    <t>13:28</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>15:28</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>08:36</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>17:04</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>11:56</t>
-  </si>
-  <si>
-    <t>15:46</t>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>15:36</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>16:49</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:47</t>
+  </si>
+  <si>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>16:37</t>
   </si>
   <si>
     <t>PKX</t>
   </si>
   <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>15:36</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:41</t>
-  </si>
-  <si>
-    <t>10:34</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>16:49</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:47</t>
-  </si>
-  <si>
-    <t>13:58</t>
-  </si>
-  <si>
-    <t>16:37</t>
-  </si>
-  <si>
     <t>00:20</t>
   </si>
   <si>
@@ -1472,9 +1490,6 @@
     <t>VN-A685</t>
   </si>
   <si>
-    <t>17:20</t>
-  </si>
-  <si>
     <t>23:55</t>
   </si>
   <si>
@@ -1502,12 +1517,6 @@
     <t>11:27</t>
   </si>
   <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1523,51 +1532,48 @@
     <t>14:09</t>
   </si>
   <si>
+    <t>VN-A698</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>VN-A699</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>5073D *</t>
+  </si>
+  <si>
+    <t>VN-A810</t>
+  </si>
+  <si>
+    <t>KZN</t>
+  </si>
+  <si>
+    <t>SVO</t>
+  </si>
+  <si>
+    <t>01:55</t>
+  </si>
+  <si>
+    <t>VN-A811</t>
+  </si>
+  <si>
+    <t>MEL</t>
+  </si>
+  <si>
     <t>16:54</t>
   </si>
   <si>
-    <t>VN-A698</t>
-  </si>
-  <si>
-    <t>08:14</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>VN-A699</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>17:08</t>
-  </si>
-  <si>
-    <t>5073D *</t>
-  </si>
-  <si>
-    <t>VN-A810</t>
-  </si>
-  <si>
-    <t>KZN</t>
-  </si>
-  <si>
-    <t>SVO</t>
-  </si>
-  <si>
-    <t>01:55</t>
-  </si>
-  <si>
-    <t>VN-A811</t>
-  </si>
-  <si>
-    <t>MEL</t>
-  </si>
-  <si>
     <t>SYD</t>
   </si>
   <si>
@@ -1637,7 +1643,7 @@
     <t>Total Record(s): 374</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 10, 2026 15:30</t>
+    <t xml:space="preserve">Generated on  Oct 10, 2026 15:51</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3504,7 +3510,9 @@
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
+      <c t="s" r="M48" s="7">
+        <v>129</v>
+      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c t="s" r="A49" s="6">
@@ -3530,10 +3538,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3563,10 +3571,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3599,7 +3607,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3608,18 +3616,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3634,13 +3642,13 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>49</v>
@@ -3654,7 +3662,7 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3669,7 +3677,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3681,15 +3689,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3704,7 +3712,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3716,10 +3724,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3737,7 +3745,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3746,13 +3754,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3770,19 +3778,19 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J57" s="7">
         <v>64</v>
@@ -3818,7 +3826,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3830,15 +3838,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c t="s" r="M59" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -3846,14 +3854,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B60" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="C60" s="7">
         <v>14</v>
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3865,10 +3873,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3886,7 +3894,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3901,14 +3909,14 @@
         <v>80</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="K61" s="7">
         <v>99</v>
       </c>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -3923,7 +3931,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3943,7 +3951,7 @@
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -3958,7 +3966,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3970,7 +3978,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>113</v>
@@ -3991,7 +3999,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -4000,13 +4008,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -4024,22 +4032,22 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -4072,7 +4080,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4081,18 +4089,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4107,27 +4115,27 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4142,7 +4150,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4151,7 +4159,7 @@
         <v>49</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I69" s="7">
         <v>127</v>
@@ -4175,22 +4183,22 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -4208,7 +4216,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4220,10 +4228,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -4241,7 +4249,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4289,7 +4297,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4298,18 +4306,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4324,13 +4332,13 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>69</v>
@@ -4344,7 +4352,7 @@
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4359,7 +4367,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4371,10 +4379,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4392,7 +4400,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4404,10 +4412,10 @@
         <v>120</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4440,7 +4448,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4452,15 +4460,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4475,7 +4483,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4487,7 +4495,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>37</v>
@@ -4495,7 +4503,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4510,7 +4518,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4525,14 +4533,14 @@
         <v>43</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="K81" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4562,7 +4570,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4571,18 +4579,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="I83" s="7">
         <v>56</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4597,27 +4605,27 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4647,7 +4655,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4667,7 +4675,7 @@
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4682,7 +4690,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4694,15 +4702,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4717,7 +4725,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4732,12 +4740,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4752,7 +4760,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4764,14 +4772,16 @@
         <v>96</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
+      <c t="s" r="M89" s="7">
+        <v>205</v>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c t="s" r="A90" s="6">
@@ -4785,7 +4795,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4797,7 +4807,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>89</v>
@@ -4829,17 +4839,17 @@
         <v>7707</v>
       </c>
       <c t="s" r="C92" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>69</v>
@@ -4862,11 +4872,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C93" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4878,7 +4888,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>127</v>
@@ -4886,7 +4896,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4901,7 +4911,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4913,10 +4923,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4934,7 +4944,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4946,10 +4956,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4982,7 +4992,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4994,15 +5004,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5017,7 +5027,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5026,13 +5036,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="I98" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5050,22 +5060,22 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5091,14 +5101,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B101" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="C101" s="7">
         <v>14</v>
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5110,17 +5120,17 @@
         <v>69</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="K101" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5135,7 +5145,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5147,10 +5157,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -5170,7 +5180,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5203,7 +5213,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5215,10 +5225,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5251,7 +5261,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5263,10 +5273,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5286,7 +5296,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5295,7 +5305,7 @@
         <v>49</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="I107" s="7">
         <v>59</v>
@@ -5306,7 +5316,7 @@
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5321,22 +5331,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5354,7 +5364,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5366,10 +5376,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5387,7 +5397,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5399,7 +5409,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>53</v>
@@ -5420,7 +5430,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5432,10 +5442,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5464,11 +5474,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C113" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5480,17 +5490,17 @@
         <v>94</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="K113" s="7">
         <v>29</v>
       </c>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5501,11 +5511,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C114" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5520,12 +5530,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5536,11 +5546,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C115" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5549,7 +5559,7 @@
         <v>69</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I115" s="7">
         <v>125</v>
@@ -5562,7 +5572,7 @@
       </c>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5573,26 +5583,26 @@
         <v>7621</v>
       </c>
       <c t="s" r="C116" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5625,7 +5635,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5637,15 +5647,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5660,7 +5670,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5669,13 +5679,13 @@
         <v>69</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5693,22 +5703,22 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5741,7 +5751,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5753,17 +5763,17 @@
         <v>49</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="K122" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -5778,7 +5788,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5787,18 +5797,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="I123" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5813,26 +5823,28 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
+      <c t="s" r="M124" s="7">
+        <v>250</v>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c t="s" r="A125" s="6">
@@ -5846,7 +5858,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5858,10 +5870,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5879,7 +5891,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5894,7 +5906,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5927,7 +5939,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5939,15 +5951,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5962,7 +5974,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5974,10 +5986,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5993,11 +6005,11 @@
         <v>2982</v>
       </c>
       <c t="s" r="C130" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6009,14 +6021,16 @@
         <v>69</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
+      <c t="s" r="M130" s="7">
+        <v>257</v>
+      </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c t="s" r="A131" s="6">
@@ -6026,11 +6040,11 @@
         <v>2982</v>
       </c>
       <c t="s" r="C131" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6039,13 +6053,13 @@
         <v>69</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -6059,17 +6073,17 @@
         <v>2983</v>
       </c>
       <c t="s" r="C132" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>69</v>
@@ -6078,7 +6092,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -6111,7 +6125,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6123,7 +6137,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>57</v>
@@ -6131,7 +6145,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6146,7 +6160,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6158,17 +6172,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>112</v>
       </c>
       <c t="s" r="K135" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6183,7 +6197,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6198,14 +6212,14 @@
         <v>37</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c t="s" r="K136" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>60</v>
+        <v>266</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6220,7 +6234,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6229,7 +6243,7 @@
         <v>49</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="I137" s="7">
         <v>106</v>
@@ -6253,13 +6267,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>49</v>
@@ -6268,7 +6282,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6286,7 +6300,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6295,13 +6309,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6334,7 +6348,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6346,7 +6360,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>32</v>
@@ -6354,7 +6368,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6369,7 +6383,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6381,7 +6395,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>91</v>
@@ -6417,7 +6431,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6429,15 +6443,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6452,7 +6466,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6464,7 +6478,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>59</v>
@@ -6472,7 +6486,7 @@
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6487,7 +6501,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6507,7 +6521,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6522,7 +6536,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6555,7 +6569,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6567,17 +6581,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>47</v>
       </c>
       <c t="s" r="K148" s="7">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>273</v>
+        <v>50</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6588,11 +6602,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C149" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6601,13 +6615,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6621,26 +6635,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C150" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6673,7 +6687,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6682,18 +6696,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6708,27 +6722,27 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6743,7 +6757,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6752,17 +6766,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
-      <c r="M154" s="7"/>
+      <c t="s" r="M154" s="7">
+        <v>128</v>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c t="s" r="A155" s="6">
@@ -6776,19 +6792,19 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>50</v>
@@ -6824,7 +6840,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6836,15 +6852,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6859,7 +6875,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6868,18 +6884,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I158" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6894,13 +6910,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>49</v>
@@ -6914,7 +6930,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6929,7 +6945,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6962,7 +6978,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6974,7 +6990,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>52</v>
@@ -6995,7 +7011,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7007,10 +7023,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -7043,7 +7059,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7055,15 +7071,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7078,7 +7094,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7090,15 +7106,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7113,7 +7129,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7133,7 +7149,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7148,7 +7164,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7163,12 +7179,12 @@
         <v>42</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7183,7 +7199,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7198,7 +7214,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7216,7 +7232,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7231,7 +7247,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -7249,7 +7265,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7261,10 +7277,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -7290,14 +7306,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B172" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7306,20 +7322,20 @@
         <v>49</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="K172" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7334,13 +7350,13 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>49</v>
@@ -7349,12 +7365,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7369,7 +7385,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7378,18 +7394,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7404,13 +7420,13 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>49</v>
@@ -7419,12 +7435,12 @@
         <v>72</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7439,7 +7455,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7448,13 +7464,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7472,13 +7488,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>49</v>
@@ -7487,7 +7503,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7520,7 +7536,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7529,18 +7545,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I179" s="7">
         <v>95</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7555,16 +7571,16 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="I180" s="7">
         <v>70</v>
@@ -7575,7 +7591,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7590,27 +7606,27 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I181" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7625,13 +7641,13 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>69</v>
@@ -7640,12 +7656,12 @@
         <v>110</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7660,7 +7676,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7672,7 +7688,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>76</v>
@@ -7693,7 +7709,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7705,10 +7721,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7741,7 +7757,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7750,18 +7766,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7776,27 +7792,27 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7811,7 +7827,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7826,12 +7842,12 @@
         <v>97</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7846,7 +7862,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7861,12 +7877,12 @@
         <v>100</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7881,7 +7897,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7893,10 +7909,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7914,7 +7930,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7926,10 +7942,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7962,7 +7978,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7971,10 +7987,10 @@
         <v>69</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>18</v>
@@ -7982,7 +7998,7 @@
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7997,27 +8013,27 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8032,7 +8048,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8047,12 +8063,12 @@
         <v>101</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8067,7 +8083,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8082,12 +8098,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8102,7 +8118,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8111,7 +8127,7 @@
         <v>69</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>44</v>
@@ -8135,13 +8151,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>69</v>
@@ -8150,7 +8166,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -8183,7 +8199,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8195,15 +8211,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8218,7 +8234,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8238,7 +8254,7 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8253,7 +8269,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8265,10 +8281,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -8301,7 +8317,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8313,15 +8329,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8336,7 +8352,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8351,12 +8367,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8371,7 +8387,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8383,7 +8399,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>100</v>
@@ -8391,7 +8407,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8406,7 +8422,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8415,7 +8431,7 @@
         <v>69</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>59</v>
@@ -8441,22 +8457,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8489,7 +8505,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8498,18 +8514,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8524,13 +8540,13 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>69</v>
@@ -8544,7 +8560,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8559,7 +8575,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8568,10 +8584,10 @@
         <v>69</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>63</v>
@@ -8592,13 +8608,13 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>69</v>
@@ -8607,7 +8623,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8640,7 +8656,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8649,18 +8665,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8675,27 +8691,27 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8710,7 +8726,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8722,7 +8738,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>100</v>
@@ -8730,7 +8746,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8745,7 +8761,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8760,12 +8776,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8780,7 +8796,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8795,7 +8811,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8813,7 +8829,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8822,20 +8838,20 @@
         <v>49</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="K220" s="7">
         <v>45</v>
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8850,13 +8866,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>49</v>
@@ -8865,14 +8881,14 @@
         <v>108</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c t="s" r="K221" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8902,7 +8918,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8922,7 +8938,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8937,7 +8953,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8949,15 +8965,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8972,7 +8988,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8984,15 +9000,15 @@
         <v>96</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9007,7 +9023,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9022,12 +9038,12 @@
         <v>33</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9042,7 +9058,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9051,10 +9067,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>37</v>
@@ -9062,7 +9078,7 @@
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9077,19 +9093,19 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>60</v>
@@ -9110,7 +9126,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9125,7 +9141,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -9143,7 +9159,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9155,10 +9171,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -9176,7 +9192,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9191,7 +9207,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9224,7 +9240,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9233,18 +9249,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9259,19 +9275,19 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>113</v>
@@ -9279,7 +9295,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9294,7 +9310,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9306,10 +9322,10 @@
         <v>120</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9342,27 +9358,27 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
+        <v>269</v>
+      </c>
+      <c t="s" r="H237" s="8">
+        <v>49</v>
+      </c>
+      <c t="s" r="I237" s="7">
+        <v>363</v>
+      </c>
+      <c t="s" r="J237" s="7">
         <v>264</v>
-      </c>
-      <c t="s" r="H237" s="8">
-        <v>49</v>
-      </c>
-      <c t="s" r="I237" s="7">
-        <v>359</v>
-      </c>
-      <c t="s" r="J237" s="7">
-        <v>260</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9377,7 +9393,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9386,13 +9402,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9410,22 +9426,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -9443,7 +9459,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9491,7 +9507,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9503,15 +9519,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9526,7 +9542,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9538,10 +9554,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9561,7 +9577,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9576,12 +9592,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9596,7 +9612,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9611,14 +9627,14 @@
         <v>98</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="K245" s="7">
         <v>99</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9633,7 +9649,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9655,7 +9671,7 @@
       </c>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9670,7 +9686,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9679,7 +9695,7 @@
         <v>69</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I247" s="7">
         <v>125</v>
@@ -9689,7 +9705,9 @@
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
-      <c r="M247" s="7"/>
+      <c t="s" r="M247" s="7">
+        <v>106</v>
+      </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c t="s" r="A248" s="6">
@@ -9703,13 +9721,13 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>69</v>
@@ -9751,7 +9769,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9760,18 +9778,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9786,27 +9804,27 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9821,7 +9839,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9830,7 +9848,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>59</v>
@@ -9841,7 +9859,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -9856,13 +9874,13 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>49</v>
@@ -9871,7 +9889,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9889,7 +9907,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9901,10 +9919,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9922,7 +9940,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9934,10 +9952,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9970,7 +9988,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9985,12 +10003,12 @@
         <v>95</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10005,7 +10023,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10014,20 +10032,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="K258" s="7">
         <v>97</v>
       </c>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10042,13 +10060,13 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>28</v>
@@ -10057,14 +10075,14 @@
         <v>124</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="K259" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10079,7 +10097,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10091,17 +10109,17 @@
         <v>49</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="K260" s="7">
         <v>59</v>
       </c>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10116,7 +10134,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10125,13 +10143,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10149,13 +10167,13 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>49</v>
@@ -10164,7 +10182,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10182,7 +10200,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10191,13 +10209,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -10215,22 +10233,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -10263,7 +10281,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -10275,7 +10293,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>71</v>
@@ -10283,7 +10301,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10298,7 +10316,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -10307,18 +10325,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10333,19 +10351,19 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>104</v>
@@ -10361,14 +10379,14 @@
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>2552</v>
+        <v>1875</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10377,58 +10395,50 @@
         <v>49</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>146</v>
-      </c>
-      <c t="s" r="K269" s="7">
-        <v>339</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="K269" s="7"/>
       <c r="L269" s="7"/>
-      <c t="s" r="M269" s="7">
-        <v>313</v>
-      </c>
+      <c r="M269" s="7"/>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c t="s" r="A270" s="6">
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>2553</v>
+        <v>1876</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>229</v>
+        <v>393</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>389</v>
-      </c>
-      <c t="s" r="K270" s="7">
-        <v>390</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="K270" s="7"/>
       <c r="L270" s="7"/>
-      <c t="s" r="M270" s="7">
-        <v>297</v>
-      </c>
+      <c r="M270" s="7"/>
     </row>
     <row r="271" ht="14.25" customHeight="1">
       <c r="A271" s="6"/>
@@ -10457,7 +10467,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10469,15 +10479,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10492,7 +10502,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10504,15 +10514,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10527,7 +10537,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10539,7 +10549,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>99</v>
@@ -10547,7 +10557,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10562,7 +10572,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10574,7 +10584,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>42</v>
@@ -10582,7 +10592,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10597,7 +10607,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10606,17 +10616,19 @@
         <v>69</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
-      <c r="M276" s="7"/>
+      <c t="s" r="M276" s="7">
+        <v>401</v>
+      </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
       <c t="s" r="A277" s="6">
@@ -10630,22 +10642,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10678,7 +10690,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10690,15 +10702,15 @@
         <v>94</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10713,7 +10725,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10725,15 +10737,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10748,7 +10760,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10757,18 +10769,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10783,13 +10795,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>69</v>
@@ -10798,12 +10810,12 @@
         <v>43</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10818,7 +10830,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10830,10 +10842,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10851,7 +10863,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10863,7 +10875,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>90</v>
@@ -10884,7 +10896,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10893,13 +10905,13 @@
         <v>69</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10932,7 +10944,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10941,18 +10953,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10967,19 +10979,19 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>18</v>
@@ -10987,7 +10999,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11002,29 +11014,29 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c t="s" r="K289" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11039,13 +11051,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>49</v>
@@ -11054,14 +11066,14 @@
         <v>98</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="K290" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11076,7 +11088,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11088,17 +11100,17 @@
         <v>96</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>43</v>
       </c>
       <c t="s" r="K291" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11113,7 +11125,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11125,7 +11137,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>128</v>
@@ -11165,7 +11177,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11174,10 +11186,10 @@
         <v>69</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>36</v>
@@ -11185,7 +11197,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11200,27 +11212,27 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11235,7 +11247,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11244,13 +11256,13 @@
         <v>69</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -11268,22 +11280,22 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -11301,7 +11313,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11310,13 +11322,13 @@
         <v>69</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11334,22 +11346,22 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11382,7 +11394,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11394,15 +11406,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11417,7 +11429,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11429,7 +11441,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>71</v>
@@ -11437,7 +11449,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11452,7 +11464,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11464,15 +11476,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11487,7 +11499,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11499,7 +11511,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>75</v>
@@ -11520,7 +11532,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11532,10 +11544,10 @@
         <v>120</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11568,7 +11580,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11577,18 +11589,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11603,13 +11615,13 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>49</v>
@@ -11618,12 +11630,12 @@
         <v>99</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11653,7 +11665,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11665,17 +11677,17 @@
         <v>69</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="K310" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11690,7 +11702,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11699,18 +11711,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11725,27 +11737,27 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11760,7 +11772,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11769,7 +11781,7 @@
         <v>69</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>43</v>
@@ -11793,13 +11805,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>69</v>
@@ -11808,7 +11820,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11841,7 +11853,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11856,12 +11868,12 @@
         <v>66</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11876,7 +11888,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11891,7 +11903,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11911,7 +11923,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11920,18 +11932,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11946,13 +11958,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>69</v>
@@ -11961,7 +11973,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11994,7 +12006,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12003,18 +12015,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12029,13 +12041,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>49</v>
@@ -12044,12 +12056,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12064,7 +12076,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12073,18 +12085,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12099,27 +12111,27 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12134,7 +12146,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12143,18 +12155,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12169,22 +12181,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12195,14 +12207,14 @@
         <v>13</v>
       </c>
       <c r="B327" s="7">
-        <v>3948</v>
+        <v>2552</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>14</v>
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12211,50 +12223,58 @@
         <v>49</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>180</v>
-      </c>
-      <c r="K327" s="7"/>
+        <v>147</v>
+      </c>
+      <c t="s" r="K327" s="7">
+        <v>450</v>
+      </c>
       <c r="L327" s="7"/>
-      <c r="M327" s="7"/>
+      <c t="s" r="M327" s="7">
+        <v>51</v>
+      </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
       <c t="s" r="A328" s="6">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>3949</v>
+        <v>2553</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>357</v>
+        <v>231</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>330</v>
-      </c>
-      <c r="K328" s="7"/>
+        <v>451</v>
+      </c>
+      <c t="s" r="K328" s="7">
+        <v>300</v>
+      </c>
       <c r="L328" s="7"/>
-      <c r="M328" s="7"/>
+      <c t="s" r="M328" s="7">
+        <v>225</v>
+      </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
       <c r="A329" s="6"/>
@@ -12283,7 +12303,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12292,18 +12312,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12333,27 +12353,27 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12368,7 +12388,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12383,12 +12403,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12403,7 +12423,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12436,7 +12456,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12448,10 +12468,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12484,7 +12504,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12493,18 +12513,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12519,27 +12539,27 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12554,7 +12574,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12569,12 +12589,12 @@
         <v>30</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12589,7 +12609,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12601,7 +12621,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>36</v>
@@ -12609,7 +12629,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12624,7 +12644,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12633,10 +12653,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>125</v>
@@ -12644,7 +12664,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12659,22 +12679,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12692,7 +12712,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12701,7 +12721,7 @@
         <v>49</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>128</v>
@@ -12725,19 +12745,19 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>48</v>
@@ -12758,7 +12778,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12770,10 +12790,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>456</v>
+        <v>393</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12806,7 +12826,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12818,7 +12838,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>110</v>
@@ -12841,7 +12861,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12853,7 +12873,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>127</v>
@@ -12861,7 +12881,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12876,7 +12896,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12891,7 +12911,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12909,7 +12929,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12921,10 +12941,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12957,7 +12977,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12966,18 +12986,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12992,27 +13012,27 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13027,7 +13047,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -13047,7 +13067,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13062,7 +13082,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13082,7 +13102,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13097,7 +13117,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13106,13 +13126,13 @@
         <v>69</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13130,22 +13150,22 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13178,7 +13198,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13187,18 +13207,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13213,13 +13233,13 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>49</v>
@@ -13233,7 +13253,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13248,7 +13268,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13257,10 +13277,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>125</v>
@@ -13283,29 +13303,29 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="K362" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13320,7 +13340,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13329,13 +13349,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>108</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13353,22 +13373,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13401,19 +13421,19 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>101</v>
@@ -13436,7 +13456,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13448,15 +13468,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13471,7 +13491,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13486,12 +13506,12 @@
         <v>125</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>105</v>
+        <v>401</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13506,7 +13526,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13518,10 +13538,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13539,7 +13559,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13551,10 +13571,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13572,7 +13592,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13620,7 +13640,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13632,15 +13652,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13655,7 +13675,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13670,12 +13690,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13690,7 +13710,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13710,7 +13730,7 @@
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13725,7 +13745,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13737,10 +13757,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13758,7 +13778,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13767,13 +13787,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13791,22 +13811,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13839,7 +13859,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13854,12 +13874,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -13874,7 +13894,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13883,18 +13903,18 @@
         <v>96</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13909,27 +13929,27 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>96</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13944,7 +13964,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13953,17 +13973,19 @@
         <v>96</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>487</v>
+        <v>250</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
-      <c r="M383" s="7"/>
+      <c t="s" r="M383" s="7">
+        <v>205</v>
+      </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
       <c t="s" r="A384" s="6">
@@ -13977,13 +13999,13 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>96</v>
@@ -13992,14 +14014,14 @@
         <v>75</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="K384" s="7">
         <v>25</v>
       </c>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14014,7 +14036,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14026,10 +14048,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -14062,7 +14084,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14074,7 +14096,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>95</v>
@@ -14082,7 +14104,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14097,7 +14119,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14109,15 +14131,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14132,7 +14154,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14141,18 +14163,18 @@
         <v>69</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14167,19 +14189,19 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>71</v>
@@ -14187,7 +14209,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14202,7 +14224,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14214,15 +14236,15 @@
         <v>94</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14237,7 +14259,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14249,10 +14271,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14270,7 +14292,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14282,17 +14304,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c t="s" r="K393" s="7">
         <v>25</v>
       </c>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14307,7 +14329,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14319,17 +14341,17 @@
         <v>69</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="K394" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14344,7 +14366,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14353,13 +14375,13 @@
         <v>69</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -14377,22 +14399,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>69</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14425,7 +14447,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14434,10 +14456,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>32</v>
@@ -14445,7 +14467,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14460,19 +14482,19 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>98</v>
@@ -14480,7 +14502,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14495,7 +14517,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14504,18 +14526,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14530,22 +14552,22 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14556,14 +14578,14 @@
         <v>13</v>
       </c>
       <c r="B402" s="7">
-        <v>1875</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C402" s="7">
         <v>14</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -14572,46 +14594,50 @@
         <v>49</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>295</v>
-      </c>
-      <c r="K402" s="7"/>
+        <v>181</v>
+      </c>
+      <c t="s" r="K402" s="7">
+        <v>169</v>
+      </c>
       <c r="L402" s="7"/>
-      <c r="M402" s="7"/>
+      <c t="s" r="M402" s="7">
+        <v>473</v>
+      </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
       <c t="s" r="A403" s="6">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B403" s="7">
-        <v>1876</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C403" s="7">
         <v>14</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>498</v>
+        <v>334</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14644,7 +14670,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14656,15 +14682,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14679,7 +14705,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14691,15 +14717,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14714,7 +14740,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14729,12 +14755,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14749,7 +14775,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14761,7 +14787,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>79</v>
@@ -14797,7 +14823,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14809,15 +14835,15 @@
         <v>69</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14832,7 +14858,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14841,10 +14867,10 @@
         <v>69</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>127</v>
@@ -14852,7 +14878,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>504</v>
+        <v>343</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14867,13 +14893,13 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>69</v>
@@ -14882,7 +14908,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14900,7 +14926,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14915,7 +14941,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14933,7 +14959,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14945,10 +14971,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>389</v>
+        <v>451</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>498</v>
+        <v>394</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14981,7 +15007,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14993,15 +15019,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15016,7 +15042,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -15025,18 +15051,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15051,13 +15077,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>49</v>
@@ -15086,7 +15112,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15098,14 +15124,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>46</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
-      <c r="M419" s="7"/>
+      <c t="s" r="M419" s="7">
+        <v>259</v>
+      </c>
     </row>
     <row r="420" ht="15" customHeight="1">
       <c t="s" r="A420" s="6">
@@ -15119,7 +15147,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15134,7 +15162,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -15152,7 +15180,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15164,10 +15192,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -15185,7 +15213,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15197,10 +15225,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -15233,7 +15261,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -15253,7 +15281,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15268,7 +15296,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -15280,7 +15308,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>60</v>
@@ -15288,7 +15316,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>511</v>
+        <v>250</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15303,7 +15331,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -15315,14 +15343,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>487</v>
+        <v>250</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>168</v>
-      </c>
-      <c r="K426" s="7"/>
+        <v>169</v>
+      </c>
+      <c t="s" r="K426" s="7">
+        <v>75</v>
+      </c>
       <c r="L426" s="7"/>
-      <c r="M426" s="7"/>
+      <c t="s" r="M426" s="7">
+        <v>76</v>
+      </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
       <c t="s" r="A427" s="6">
@@ -15336,7 +15368,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15348,14 +15380,18 @@
         <v>49</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>108</v>
       </c>
-      <c r="K427" s="7"/>
+      <c t="s" r="K427" s="7">
+        <v>316</v>
+      </c>
       <c r="L427" s="7"/>
-      <c r="M427" s="7"/>
+      <c t="s" r="M427" s="7">
+        <v>131</v>
+      </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
       <c r="A428" s="6"/>
@@ -15377,36 +15413,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B429" s="7">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c t="s" r="C429" s="7">
         <v>14</v>
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c t="s" r="K429" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15417,17 +15453,17 @@
         <v>5074</v>
       </c>
       <c t="s" r="C430" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>94</v>
@@ -15436,7 +15472,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -15454,7 +15490,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
@@ -15466,10 +15502,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -15502,29 +15538,29 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="K433" s="7">
         <v>99</v>
       </c>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>504</v>
+        <v>520</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15539,7 +15575,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
@@ -15548,20 +15584,20 @@
         <v>49</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c t="s" r="K434" s="7">
         <v>51</v>
       </c>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15587,11 +15623,11 @@
         <v>5071</v>
       </c>
       <c t="s" r="C436" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -15600,7 +15636,7 @@
         <v>94</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c t="s" r="I436" s="7">
         <v>111</v>
@@ -15609,11 +15645,11 @@
         <v>46</v>
       </c>
       <c t="s" r="K436" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15628,13 +15664,13 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>94</v>
@@ -15643,14 +15679,14 @@
         <v>107</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c t="s" r="K437" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15680,7 +15716,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
@@ -15692,15 +15728,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15711,11 +15747,11 @@
         <v>2840</v>
       </c>
       <c t="s" r="C440" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15724,10 +15760,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>46</v>
@@ -15735,7 +15771,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15746,17 +15782,17 @@
         <v>2841</v>
       </c>
       <c t="s" r="C441" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>16</v>
@@ -15765,7 +15801,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15798,27 +15834,27 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>94</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15833,7 +15869,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
@@ -15848,14 +15884,14 @@
         <v>72</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="K444" s="7">
         <v>72</v>
       </c>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15870,7 +15906,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
@@ -15882,17 +15918,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="K445" s="7">
         <v>44</v>
       </c>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -15907,7 +15943,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15916,20 +15952,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c t="s" r="K446" s="7">
         <v>108</v>
       </c>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15944,13 +15980,13 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>16</v>
@@ -15959,14 +15995,14 @@
         <v>90</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c t="s" r="K447" s="7">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15996,7 +16032,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
@@ -16005,10 +16041,10 @@
         <v>69</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>84</v>
@@ -16016,7 +16052,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16031,22 +16067,22 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c t="s" r="I450" s="7">
         <v>112</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -16064,22 +16100,22 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G451" s="8">
+        <v>538</v>
+      </c>
+      <c t="s" r="H451" s="8">
         <v>536</v>
       </c>
-      <c t="s" r="H451" s="8">
-        <v>534</v>
-      </c>
       <c t="s" r="I451" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -16112,7 +16148,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
@@ -16121,18 +16157,18 @@
         <v>49</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16147,22 +16183,22 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -16170,7 +16206,7 @@
     </row>
     <row r="455" ht="16.5" customHeight="1">
       <c t="s" r="A455" s="9">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
@@ -16190,7 +16226,7 @@
     <row r="456" ht="65.25" customHeight="1"/>
     <row r="457" ht="16.5" customHeight="1">
       <c t="s" r="A457" s="10">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B457" s="10"/>
       <c r="C457" s="10"/>
@@ -16203,7 +16239,7 @@
       <c r="J457" s="10"/>
       <c r="K457" s="10"/>
       <c t="s" r="L457" s="11">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M457" s="11"/>
       <c r="N457" s="11"/>
